--- a/data_exchange_nomenclature_prices_report.xlsx
+++ b/data_exchange_nomenclature_prices_report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Тарифы" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,17 +27,31 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +59,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,490 +434,608 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Номенклатура</t>
+          <t>Услуга</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Санкт-Петербург</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Республика Татарстан</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Новосибирская обл.</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Свердловская обл.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ЕГАИС</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ЕГАИС (алкоголь) — Базовый</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Egais</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ЕГАИС (алкоголь) — Опт</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Egais_opt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ЕГАИС (алкоголь) — Профи</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Egais_prof</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Меркурий</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Меркурий (мясо, молочка) — Базовый</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mercury</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Меркурий (мясо, молочка) — Опт</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mercury_opt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Меркурий (мясо, молочка) — Профи</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mercury_prof</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Маркировка</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Маркировка лекарств</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Marking_f</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Маркировка лекарств — доп. пакет</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Add_farma</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Egais</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Egais_opt</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Egais_prof</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>8 500</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>8 500</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8 500</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>8 500</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>8 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Маркировка остатков</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Marking_ost</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Маркировка ювелирных изделий (Saby Retail)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dmdk</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Маркировка — Базовый</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Marking</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Marking_f</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>10 000</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>10 000</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>10 000</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>10 000</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>10 000</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Маркировка — Опт</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Marking_opt</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Marking_ost</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Маркировка — Профи</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Marking_prof</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>13 500</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>13 500</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>13 500</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>13 500</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>13 500</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Mercury</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Mercury_opt</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>7 000</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Mercury_prof</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>8 500</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>8 500</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>8 500</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>8 500</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>8 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Прослеживаемость</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Прослеживаемость кодов партий (налоговая)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Tracking</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>5 500</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>5 500</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>5 500</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>5 500</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>5 500</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dmdk</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A18:G18"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_exchange_nomenclature_prices_report.xlsx
+++ b/data_exchange_nomenclature_prices_report.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:CN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,91 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="15" customWidth="1" min="35" max="35"/>
+    <col width="15" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="15" customWidth="1" min="39" max="39"/>
+    <col width="15" customWidth="1" min="40" max="40"/>
+    <col width="15" customWidth="1" min="41" max="41"/>
+    <col width="15" customWidth="1" min="42" max="42"/>
+    <col width="15" customWidth="1" min="43" max="43"/>
+    <col width="15" customWidth="1" min="44" max="44"/>
+    <col width="15" customWidth="1" min="45" max="45"/>
+    <col width="15" customWidth="1" min="46" max="46"/>
+    <col width="15" customWidth="1" min="47" max="47"/>
+    <col width="15" customWidth="1" min="48" max="48"/>
+    <col width="15" customWidth="1" min="49" max="49"/>
+    <col width="15" customWidth="1" min="50" max="50"/>
+    <col width="15" customWidth="1" min="51" max="51"/>
+    <col width="15" customWidth="1" min="52" max="52"/>
+    <col width="15" customWidth="1" min="53" max="53"/>
+    <col width="15" customWidth="1" min="54" max="54"/>
+    <col width="15" customWidth="1" min="55" max="55"/>
+    <col width="15" customWidth="1" min="56" max="56"/>
+    <col width="15" customWidth="1" min="57" max="57"/>
+    <col width="15" customWidth="1" min="58" max="58"/>
+    <col width="15" customWidth="1" min="59" max="59"/>
+    <col width="15" customWidth="1" min="60" max="60"/>
+    <col width="15" customWidth="1" min="61" max="61"/>
+    <col width="15" customWidth="1" min="62" max="62"/>
+    <col width="15" customWidth="1" min="63" max="63"/>
+    <col width="15" customWidth="1" min="64" max="64"/>
+    <col width="15" customWidth="1" min="65" max="65"/>
+    <col width="15" customWidth="1" min="66" max="66"/>
+    <col width="15" customWidth="1" min="67" max="67"/>
+    <col width="15" customWidth="1" min="68" max="68"/>
+    <col width="15" customWidth="1" min="69" max="69"/>
+    <col width="15" customWidth="1" min="70" max="70"/>
+    <col width="15" customWidth="1" min="71" max="71"/>
+    <col width="15" customWidth="1" min="72" max="72"/>
+    <col width="15" customWidth="1" min="73" max="73"/>
+    <col width="15" customWidth="1" min="74" max="74"/>
+    <col width="15" customWidth="1" min="75" max="75"/>
+    <col width="15" customWidth="1" min="76" max="76"/>
+    <col width="15" customWidth="1" min="77" max="77"/>
+    <col width="15" customWidth="1" min="78" max="78"/>
+    <col width="15" customWidth="1" min="79" max="79"/>
+    <col width="15" customWidth="1" min="80" max="80"/>
+    <col width="15" customWidth="1" min="81" max="81"/>
+    <col width="15" customWidth="1" min="82" max="82"/>
+    <col width="15" customWidth="1" min="83" max="83"/>
+    <col width="15" customWidth="1" min="84" max="84"/>
+    <col width="15" customWidth="1" min="85" max="85"/>
+    <col width="15" customWidth="1" min="86" max="86"/>
+    <col width="15" customWidth="1" min="87" max="87"/>
+    <col width="15" customWidth="1" min="88" max="88"/>
+    <col width="15" customWidth="1" min="89" max="89"/>
+    <col width="15" customWidth="1" min="90" max="90"/>
+    <col width="15" customWidth="1" min="91" max="91"/>
+    <col width="15" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,17 +554,442 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Республика Адыгея</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Бурятия</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Алтай</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Дагестан</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Ингушетия</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Респ. Кабардино-Балкарская</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Калмыкия</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Респ. Карачаево-Черкесская</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Карелия</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Коми</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Марий Эл</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Мордовия</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Саха (Якутия)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Северная Осетия - Алания</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Республика Татарстан</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Тыва</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Удмуртская Республика</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Хакасия</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Чечня</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Чувашия</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Алтайский край</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Краснодарский край</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Красноярский край</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Приморский край</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Ставропольский край</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Хабаровский край</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Амурская обл.</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Архангельская обл.</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Астраханская обл.</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Белгородская обл.</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Брянская обл.</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Владимирская обл.</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Волгоградская обл.</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Вологодская обл.</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Воронежская обл.</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Ивановская обл.</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Иркутская обл.</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Калининградская обл.</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Калужская обл.</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Камчатский край</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Кемеровская обл.</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Кировская обл.</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Костромская обл.</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Курганская обл.</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Курская обл.</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Ленинградская обл.</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Липецкая обл.</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Магаданская обл.</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Московская обл.</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Мурманская обл.</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Нижегородская обл.</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Новгородская обл.</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Новосибирская обл.</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Омская обл.</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Оренбургская обл.</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Орловская обл.</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Пензенская обл.</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Пермский край</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Псковская обл.</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Ростовская обл.</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Рязанская обл.</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Самарская обл.</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Тольятти</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>Саратовская обл.</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>Сахалинская обл.</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Свердловская обл.</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>Смоленская обл.</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>Тамбовская обл.</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>Тверская обл.</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>Томская обл.</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>Тульская обл.</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>Тюменская обл.</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>Ульяновская обл.</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Челябинская обл.</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Забайкальский край</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Ярославская обл.</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Еврейская АО</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Ненецкий АО</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>Ханты-Мансийский АО</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Чукотский АО</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>Ямало-Ненецкий АО</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Запорожская обл.</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>Республика Крым</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>Севастополь</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>Донецкая нар. респ.</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>Луганская нар. респ.</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>Херсонская обл.</t>
         </is>
       </c>
     </row>
@@ -526,6 +1036,431 @@
           <t>4 000</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -563,6 +1498,431 @@
           <t>7 000</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -600,6 +1960,431 @@
           <t>8 500</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -644,6 +2429,431 @@
           <t>4 000</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -681,6 +2891,431 @@
           <t>7 000</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -718,6 +3353,431 @@
           <t>8 500</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>8 500</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -762,6 +3822,431 @@
           <t>10 000</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,6 +4284,431 @@
           <t>7 000</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -836,6 +4746,431 @@
           <t>7 000</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CK13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CL13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CM13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CN13" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -873,6 +5208,431 @@
           <t>15 000</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CK14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CL14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CM14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="CN14" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -910,6 +5670,431 @@
           <t>4 000</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CK15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CL15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CM15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="CN15" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -947,6 +6132,431 @@
           <t>7 000</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CJ16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CK16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CL16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CM16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="CN16" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -984,6 +6594,431 @@
           <t>13 500</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CK17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CL17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CM17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="CN17" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1028,13 +7063,438 @@
           <t>5 500</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CK19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CL19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CM19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="CN19" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A18:CN18"/>
+    <mergeCell ref="A6:CN6"/>
+    <mergeCell ref="A2:CN2"/>
+    <mergeCell ref="A10:CN10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
